--- a/task5_judge_results.xlsx
+++ b/task5_judge_results.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="joint_full_run" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="manual_joint_compare" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="manual_single_compare" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,65 +512,60 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>experiment_type</t>
+          <t>joint_judge_model</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>baseline_model</t>
+          <t>fluency_judge_explanation</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>fluency_judge_explanation</t>
+          <t>fluency_judge_verdict</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>fluency_judge_verdict</t>
+          <t>grammar_judge_explanation</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>grammar_judge_explanation</t>
+          <t>grammar_judge_verdict</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>grammar_judge_verdict</t>
+          <t>tone_judge_explanation</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>tone_judge_explanation</t>
+          <t>tone_judge_verdict</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>tone_judge_verdict</t>
+          <t>length_judge_explanation</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>length_judge_explanation</t>
+          <t>length_judge_verdict</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>length_judge_verdict</t>
+          <t>grounding_judge_explanation</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>grounding_judge_explanation</t>
+          <t>grounding_judge_verdict</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
-        <is>
-          <t>grounding_judge_verdict</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
         <is>
           <t>judge_final_score</t>
         </is>
@@ -601,17 +599,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Experience the power and elegance of the Apple iPhone 15 Pro.  Equipped with the blazing-fast A17 Pro chip and a stunning 120Hz ProMotion display, this compact phone delivers a seamless and immersive experience.  Crafted with a durable titanium frame and Ceramic Shield glass, the iPhone 15 Pro is built to last.  Enjoy the convenience of USB-C fast charging and peace of mind with Apple's 1-year limited warranty.</t>
+          <t>Experience the power and elegance of the iPhone 15 Pro.  Fueled by the blazing-fast A17 Pro chip and boasting a stunning 120Hz ProMotion display, this compact powerhouse delivers an unparalleled user experience.  Crafted with a durable titanium frame and protective Ceramic Shield glass, the iPhone 15 Pro is built to last. Plus, enjoy the convenience of USB-C fast charging. Backed by a 1-year limited warranty, the iPhone 15 Pro is the ultimate choice for discerning users.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2287</v>
+        <v>1914</v>
       </c>
       <c r="H2" t="n">
-        <v>291</v>
+        <v>207</v>
       </c>
       <c r="I2" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -640,12 +638,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -654,69 +652,64 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1.863e-05</v>
+        <v>1.656e-05</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., "Experience the power and elegance of the iPhone 15 Pro."</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally, with clear flow and no awkward phrasing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>No punctuation or spelling errors are evident, such as the correct hyphenation in "blazing-fast".</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>There are no spelling, punctuation, or grammatical errors.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The language is product‑focused and credible, but phrases like "blazing‑fast" and "ultimate choice" add mild hype.</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>The tone is friendly, credible, and persuasive, suitable for e‑commerce product marketing.</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 76 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The description contains 66 words, which falls within the 50‑90 word target range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>All concrete claims match the source data: "A17 Pro chip", "120Hz ProMotion display", "compact", "titanium frame", "Ceramic Shield glass", "USB‑C fast charging", and "1‑year limited warranty".</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>All claims (A17 Pro chip, 120 Hz ProMotion display, compact size, titanium frame, Ceramic Shield glass, USB‑C fast charging, and 1‑year limited warranty) are directly supported by the provided product information.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -725,17 +718,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sony WH‑1000XM5 Headphones</t>
+          <t>Samsung Galaxy S24 Ultra</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>features: active noise cancelling, 30 hr battery, Bluetooth 5.2; capacity: large</t>
+          <t>features: 200 MP camera, S‑Pen support, 120 Hz AMOLED; sustainably sourced</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>synthetic leather earcups</t>
+          <t>Armor Aluminum frame, Gorilla Glass Victus</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -750,43 +743,23 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Escape into your music with the Sony WH-1000XM5 Headphones.  These headphones feature industry-leading active noise cancelling to block out distractions, allowing you to fully immerse yourself in your audio. Enjoy up to 30 hours of battery life on a single charge and seamless connectivity with Bluetooth 5.2.  Crafted with synthetic leather earcups for a comfortable fit, the WH-1000XM5 Headphones are backed by a 1-year limited warranty.</t>
+          <t>Capture life's moments in stunning detail with the Samsung Galaxy S24 Ultra's revolutionary 200MP camera.  Experience smooth scrolling and vibrant visuals on the 120Hz AMOLED display, enhanced by the precision of S Pen support.  Crafted with a durable Armor Aluminum frame and Gorilla Glass Victus, this phone is built to last. Plus, enjoy peace of mind with a 1-year limited warranty.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1240</v>
+        <v>1159</v>
       </c>
       <c r="H3" t="n">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="I3" t="n">
-        <v>105</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>good</t>
@@ -797,75 +770,66 @@
           <t>good</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.851e-05</v>
+        <v>1.467e-05</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., “Capture life's moments in stunning detail with the Samsung Galaxy S24 Ultra's revolutionary 200MP camera.”</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally, with clear flow and easy to understand sentences.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>No punctuation, spelling, or agreement errors are present; the sentence structure is correct throughout.</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>There are no grammatical, spelling, or punctuation errors.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The language is product‑focused and persuasive without exaggeration, such as “Enjoy peace of mind with a 1‑year limited warranty.”</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>The tone is friendly, persuasive, and suitable for e‑commerce, highlighting benefits and features.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 61 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The description contains 66 words, which falls within the 50‑90 word range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>All concrete claims match the source data: “200MP camera,” “120Hz AMOLED display,” “S Pen support,” “Armor Aluminum frame and Gorilla Glass Victus,” and “1‑year limited warranty.”</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>All claims (active noise cancelling, 30 hr battery, Bluetooth 5.2, synthetic leather earcups, 1‑year limited warranty) are directly supported by the provided product data, with no added or altered information.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -874,17 +838,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amazon Echo Dot (5th Gen)</t>
+          <t>Google Pixel 8 Pro</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>features: Alexa voice assistant, temperature sensor, improved bass; sustainably sourced</t>
+          <t>features: Tensor G3 chip, Magic Eraser, 50 MP camera; rating: 4.7/5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>recycled fabric mesh</t>
+          <t>matte glass back, aluminum frame</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -899,43 +863,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meet the new Amazon Echo Dot (5th Gen), featuring the Alexa voice assistant for hands-free control of your smart home.  This compact device boasts an improved bass for richer sound and includes a temperature sensor for added convenience.  Crafted with sustainably sourced, recycled fabric mesh, the Echo Dot (5th Gen) is both stylish and eco-friendly. Your purchase is backed by a 1-year limited warranty.</t>
+          <t>Capture life's magic with the Google Pixel 8 Pro. Powered by the cutting-edge Tensor G3 chip, this phone delivers incredible performance and features like the groundbreaking Magic Eraser for effortless photo editing.  Its stunning 50MP camera ensures every moment is captured in vibrant detail.  Crafted with a sleek matte glass back and durable aluminum frame, the Pixel 8 Pro is both beautiful and reliable, backed by a 1-year limited warranty.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1233</v>
+        <v>1192</v>
       </c>
       <c r="H4" t="n">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="I4" t="n">
-        <v>90</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>good</t>
@@ -943,97 +887,88 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>1.744e-05</v>
+        <v>1.485e-05</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, but the repeated double space after the first sentence (“...photo editing.  Its stunning...”) is slightly awkward.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>The description reads smoothly, uses natural phrasing, and is easy to understand.</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>No spelling or punctuation errors are present; the sentence structure is correct.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>There are no spelling, punctuation, or grammatical errors.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>Phrases like “groundbreaking Magic Eraser” and “incredible performance” are mildly overhyped, making the tone somewhat promotional rather than strictly factual.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>The tone is friendly, credible, and persuasive, suitable for e‑commerce product marketing.</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 69 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The description contains 64 words, which falls within the 50‑90 word target range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>All concrete claims—Tensor G3 chip, Magic Eraser, 50 MP camera, matte glass back, aluminum frame, 1‑year limited warranty—match the provided product data.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>All claims (Alexa voice assistant, temperature sensor, improved bass, sustainably sourced, recycled fabric mesh, 1‑year limited warranty) are directly supported by the provided product information.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fitbit Charge 6</t>
+          <t>Sony WH‑1000XM5 Headphones</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>features: heart‑rate monitor, built‑in GPS, 7‑day battery; color options: multiple</t>
+          <t>features: active noise cancelling, 30 hr battery, Bluetooth 5.2; capacity: large</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>aluminum case</t>
+          <t>synthetic leather earcups</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1048,17 +983,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The Fitbit Charge 6 is your stylish and reliable fitness companion. Featuring a heart-rate monitor, built-in GPS, and a 7-day battery life, it tracks your activity and progress with ease.  Choose from multiple color options to find the perfect fit for your style, all housed in a sleek aluminum case. Backed by a 1-year limited warranty, the Charge 6 is ready to help you reach your health goals.</t>
+          <t>Escape into your own world of sound with the Sony WH-1000XM5 Headphones.  These premium headphones boast industry-leading active noise cancelling, so you can focus on your music, podcast, or audiobook without distractions. Enjoy up to 30 hours of battery life on a single charge and seamless Bluetooth 5.2 connectivity.  Crafted with comfortable synthetic leather earcups, the XM5s are perfect for extended listening sessions.  Backed by a 1-year limited warranty, you can experience audio excellence with confidence.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1049</v>
+        <v>1410</v>
       </c>
       <c r="H5" t="n">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="I5" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1077,93 +1012,88 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1.864e-05</v>
+        <v>1.647e-05</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., "Escape into your own world of sound with the Sony WH-1000XM5 Headphones."</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally, with a clear flow of ideas.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>There are no noticeable errors; the sentence "Backed by a 1-year limited warranty, you can experience audio excellence with confidence." is grammatically correct.</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>There are no spelling, punctuation, or grammatical errors.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The tone is friendly and credible, focusing on product features without exaggeration, such as "industry-leading active noise cancelling" which is a common claim for this model.</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>The tone is friendly, persuasive, and appropriate for an e‑commerce product description.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 76 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The description contains about 68 words, which falls within the 50–90 word range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>All concrete claims match the source data: "active noise cancelling", "30 hours of battery life", "Bluetooth 5.2", "synthetic leather earcups", and "1‑year limited warranty" are directly stated in the description.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>All claims (heart‑rate monitor, built‑in GPS, 7‑day battery, multiple color options, aluminum case, 1‑year limited warranty) are directly supported by the provided product data.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1172,17 +1102,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DJI Mini 4 Pro Drone</t>
+          <t>Bose QuietComfort Ultra Earbuds</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>features: 4K/60fps, omnidirectional obstacle sensing, &lt;250 g; rating: 4.7/5</t>
+          <t>features: CustomTune sound calibration, ANC, IPX4; award‑winning design</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>composite plastic</t>
+          <t>silicone ear tips</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1197,43 +1127,23 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Capture stunning 4K video at 60fps with the DJI Mini 4 Pro drone.  Weighing under 250g, this compact drone features omnidirectional obstacle sensing for safe and effortless flight.  Crafted from durable composite plastic, the Mini 4 Pro comes with a 1-year limited warranty, ensuring peace of mind for your aerial adventures.</t>
+          <t>Experience unparalleled comfort and sound with the award-winning Bose QuietComfort Ultra Earbuds.  These earbuds feature CustomTune technology for a personalized listening experience and powerful noise cancellation to block out distractions.  With an IPX4 water resistance rating and comfortable silicone ear tips, they're perfect for your active lifestyle. Backed by a 1-year limited warranty, enjoy peace of mind with your purchase.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>991</v>
+        <v>1090</v>
       </c>
       <c r="H6" t="n">
-        <v>291</v>
+        <v>193</v>
       </c>
       <c r="I6" t="n">
-        <v>81</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>good</t>
@@ -1244,75 +1154,66 @@
           <t>good</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>1.62e-05</v>
+        <v>1.335e-05</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., "Experience unparalleled comfort and sound with the award-winning Bose QuietComfort Ultra Earbuds."</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally without awkward phrasing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>No spelling, punctuation, or grammatical errors are present, such as the correct sentence "Backed by a 1-year limited warranty, enjoy peace of mind with your purchase."</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>There are no spelling, punctuation, or grammatical errors.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The tone is friendly and credible, focusing on product features without exaggerated hype, e.g., "perfect for your active lifestyle."</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>The tone is friendly, credible, and persuasive, suitable for e‑commerce marketing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 60 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The description contains 49 words, which falls into the 40‑49 word range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>All claims match the provided data: CustomTune technology, ANC, IPX4, silicone ear tips, award‑winning design, and a 1‑year limited warranty are directly referenced.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>All claims (4K/60fps, omnidirectional obstacle sensing, weight &lt;250 g, composite plastic, 1‑year limited warranty) are directly supported by the provided product data.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1321,17 +1222,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Xbox Series X</t>
+          <t>Amazon Echo Dot (5th Gen)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>features: 12 TFLOPS GPU, 1 TB SSD, 4K @ 120 Hz; battery: long‑lasting</t>
+          <t>features: Alexa voice assistant, temperature sensor, improved bass; sustainably sourced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>matte black casing</t>
+          <t>recycled fabric mesh</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1346,17 +1247,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Experience next-gen gaming with the Xbox Series X.  Powered by a 12 TFLOPS GPU and a 1TB SSD, this console delivers stunning 4K visuals at up to 120Hz for incredibly smooth gameplay.  The sleek matte black casing adds a touch of modern style to your entertainment setup, while the long-lasting battery ensures hours of uninterrupted gaming. Your purchase is backed by a 1-year limited warranty for peace of mind.</t>
+          <t>Meet the new Echo Dot, packed with smart features and sustainable style.  
+With Alexa, you can control your smart home, play music, get answers to questions, and more, all with just your voice. This 5th generation Echo Dot boasts an improved bass for richer sound and even includes a temperature sensor for added convenience. Plus, it's crafted with a cozy recycled fabric mesh, making it a responsible choice for your home.  Enjoy peace of mind with a 1-year limited warranty.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1059</v>
+        <v>1326</v>
       </c>
       <c r="H7" t="n">
-        <v>291</v>
+        <v>193</v>
       </c>
       <c r="I7" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1365,7 +1267,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1375,22 +1277,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>good</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1399,69 +1301,64 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1.728e-05</v>
+        <v>1.551e-05</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., “Meet the new Echo Dot, packed with smart features and sustainable style.” No awkward or repetitive phrasing is present.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally without awkward phrasing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>There are no noticeable spelling, punctuation, or grammatical errors; the sentence structure is correct throughout.</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>No spelling, punctuation, or grammatical errors are present.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The tone is friendly and product‑focused, highlighting features without exaggerated hype, such as “Enjoy peace of mind with a 1‑year limited warranty.”</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>The tone is friendly, persuasive, and appropriate for e‑commerce product marketing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 79 words, which falls within the 50‑90 word target range.</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>The description contains 69 words, which falls within the 50–90 word range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>All concrete claims match the source data: “improved bass,” “temperature sensor,” “recycled fabric mesh,” and “1‑year limited warranty” are all directly listed in the attributes.</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>All claims about the GPU, SSD, 4K @ 120 Hz, matte black casing, long‑lasting battery, and 1‑year limited warranty are directly supported by the provided product data.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1470,22 +1367,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Instant Pot Duo 6‑Quart</t>
+          <t>Dell XPS 13 9310 Laptop</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>features: 7‑in‑1 multicooker, stainless steel inner pot, 1000 W heating; weight: light</t>
+          <t>features: 13.4″ FHD+ display, Intel Core i5, Thunderbolt 4; dimensions: compact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18/8 stainless steel</t>
+          <t>CNC aluminum &amp; carbon‑fiber palmrest</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1‑year limited warranty</t>
+          <t>1‑year limited hardware warranty</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1495,122 +1392,93 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The Instant Pot Duo 6-Quart is a versatile 7-in-1 multicooker that makes meal prep a breeze.  Featuring a durable 18/8 stainless steel inner pot and a powerful 1000W heating element, this lightweight appliance is perfect for busy kitchens.  Backed by a 1-year limited warranty, the Instant Pot Duo is a reliable choice for all your cooking needs.</t>
+          <t>Experience effortless productivity with the Dell XPS 13 9310. Its stunning 13.4″ FHD+ display brings your work to life, while the powerful Intel Core i5 processor handles demanding tasks with ease.  Seamlessly connect to peripherals and enjoy blazing-fast data transfer speeds with Thunderbolt 4.  Crafted from premium CNC aluminum and a sleek carbon-fiber palmrest, the XPS 13 9310 is both durable and stylish. Plus, enjoy peace of mind with a 1-year limited hardware warranty.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1115</v>
+        <v>1766</v>
       </c>
       <c r="H8" t="n">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="I8" t="n">
-        <v>92</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>2.108e-05</v>
+        <v>1.728e-05</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The sentence "while the powerful Intel Core i5 processor handles demanding tasks with ease" reads smoothly without any awkward phrasing.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally without awkward phrasing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains no noticeable spelling, punctuation, or grammatical errors, e.g., "Crafted from premium CNC aluminum and a sleek carbon-fiber palmrest".</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>There are no spelling, punctuation, or grammatical errors.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The language is friendly and credible, focusing on product features without exaggeration, such as "Enjoy peace of mind with a 1-year limited hardware warranty."</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>The tone is friendly, credible, and persuasive, suitable for e‑commerce marketing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 73 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>The description contains 57 words, which falls within the 50‑90 word target range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The claim "13.4″ FHD+ display" matches the listed feature, and "CNC aluminum &amp; carbon-fiber palmrest" matches the material attribute, with all other features directly supported by the provided data.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>All claims (7‑in‑1 multicooker, 18/8 stainless steel inner pot, 1000 W heating element, lightweight, 1‑year limited warranty) are directly supported by the provided product data.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1619,22 +1487,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LEGO Star Wars Millennium Falcon 75192</t>
+          <t>Apple MacBook Air 13″ (M3)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>features: 7 541 pieces, detailed interior, minifigs included; battery: long‑lasting</t>
+          <t>features: M3 chip, 18‑hour battery, 1080p camera; energy efficient</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ABS plastic bricks</t>
+          <t>recycled aluminum unibody</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lifetime replacement of missing bricks</t>
+          <t>1‑year limited warranty</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1644,122 +1512,93 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Build the iconic Millennium Falcon with this incredible 7,541-piece LEGO set!  Explore a detailed interior and bring your favorite Star Wars characters to life with the included minifigures.  Crafted from durable ABS plastic bricks, this set comes with a lifetime warranty ensuring you can always replace any missing bricks.</t>
+          <t>Experience effortless performance and all-day productivity with the new MacBook Air 13" (M3). Powered by the innovative M3 chip, this sleek laptop boasts incredible energy efficiency and a stunning 1080p camera for crystal-clear video calls. Enjoy up to 18 hours of battery life on a single charge, perfect for staying connected wherever you go. Crafted from a durable recycled aluminum unibody, the MacBook Air is both stylish and sustainable. Backed by a 1-year limited warranty, you can be confident in your investment.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>890</v>
+        <v>1569</v>
       </c>
       <c r="H9" t="n">
-        <v>287</v>
+        <v>207</v>
       </c>
       <c r="I9" t="n">
-        <v>69</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>118</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>bad</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>1.721e-05</v>
+        <v>1.683e-05</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., "Experience effortless performance and all‑day productivity with the new MacBook Air 13".</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally without awkward phrasing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>No punctuation, spelling, or agreement errors are present, such as the correct use of commas and hyphens throughout.</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>No grammar, spelling, or punctuation errors are present.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The language is product‑focused and persuasive without exaggerated hype, e.g., “Backed by a 1‑year limited warranty, you can be confident in your investment.”</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>The tone is friendly, credible, and persuasive, suitable for e-commerce marketing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 81 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>The description contains 49 words, which falls into the 40‑49 word range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>All concrete claims match the source data: “M3 chip,” “up to 18 hours of battery life,” “1080p camera,” “energy efficiency,” “recycled aluminum unibody,” and “1‑year limited warranty.”</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>All claims (piece count, detailed interior, minifigures, ABS plastic, lifetime warranty) are directly supported by the product data.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1768,17 +1607,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eufy Video Doorbell Dual</t>
+          <t>Microsoft Surface Pro 10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>features: dual camera, package detection, 2K resolution; battery: long‑lasting</t>
+          <t>features: Intel Core Ultra, detachable keyboard, 13″ PixelSense; dimensions: compact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>plastic housing</t>
+          <t>magnesium alloy chassis</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1793,43 +1632,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>See everything with the Eufy Video Doorbell Dual, featuring two cameras for a wider view and package detection to alert you when deliveries arrive.  Enjoy crisp 2K resolution and the convenience of a long-lasting battery. This doorbell comes with a 1-year limited warranty and is housed in durable plastic.</t>
+          <t>The Microsoft Surface Pro 10 is the ultimate portable powerhouse.  Boasting an Intel Core Ultra processor and a stunning 13" PixelSense display, it delivers incredible performance and crystal-clear visuals.  Its compact design and detachable keyboard make it perfect for working on the go, while the durable magnesium alloy chassis ensures lasting reliability.  Backed by a 1-year limited warranty, the Surface Pro 10 is your perfect companion for productivity and entertainment.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>950</v>
+        <v>1186</v>
       </c>
       <c r="H10" t="n">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="I10" t="n">
-        <v>68</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>bad</t>
-        </is>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>good</t>
@@ -1840,75 +1659,66 @@
           <t>good</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>1.806e-05</v>
+        <v>1.479e-05</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., "The Microsoft Surface Pro 10 is the ultimate portable powerhouse."</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally without awkward phrasing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>There are no spelling, punctuation, or grammatical errors, such as the correctly placed commas in "Boasting an Intel Core Ultra processor and a stunning 13" PixelSense display, it delivers..."</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>There are no spelling, punctuation, or grammatical errors.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The language uses hype phrases like "ultimate portable powerhouse" and "incredible performance," which is slightly over‑promotional.</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>The tone is friendly, credible, and persuasive, suitable for e‑commerce marketing.</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 70 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>The description contains 49 words, which falls into the 40‑49 word range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>All claims—Intel Core Ultra processor, 13" PixelSense display, detachable keyboard, compact design, magnesium alloy chassis, and 1‑year limited warranty—are directly supported by the product data.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>All claims (dual camera, package detection, 2K resolution, long‑lasting battery, plastic housing, 1‑year limited warranty) are directly supported by the provided product information.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1917,9 +1727,6560 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Garmin Forerunner 255</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>features: multi‑band GPS, HRV status, 14‑day battery; rating: 4.7/5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fiber‑reinforced polymer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Elevate your running with the Garmin Forerunner 255. This lightweight, fiber-reinforced polymer watch boasts multi-band GPS for precise tracking and HRV status to monitor your recovery.  Enjoy up to 14 days of battery life, perfect for long training weeks.  Don't just take our word for it, see why runners love the Forerunner 255 with a 4.7/5 star rating. Backed by a 1-year limited warranty, it's the smart choice for serious athletes.</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1729</v>
+      </c>
+      <c r="H11" t="n">
+        <v>205</v>
+      </c>
+      <c r="I11" t="n">
+        <v>116</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1.659e-05</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Enjoy up to 14 days of battery life, perfect for long training weeks.”</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>The copy is friendly and product‑focused without exaggerated hype, such as “Elevate your running with the Garmin Forerunner 255.”</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>The description contains 71 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “multi‑band GPS”, “HRV status”, “up to 14 days of battery life”, “fiber‑reinforced polymer”, “4.7/5 star rating”, and “1‑year limited warranty”.</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fitbit Charge 6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>features: heart‑rate monitor, built‑in GPS, 7‑day battery; color options: multiple</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>aluminum case</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stay on top of your health and fitness goals with the Fitbit Charge 6. This sleek aluminum tracker features a built-in GPS to accurately map your runs and walks, plus a heart-rate monitor to keep tabs on your exertion. Enjoy up to 7 days of battery life on a single charge, so you can focus on your activity, not your charger.  Choose from multiple color options to find the perfect fit for your style.  Backed by a 1-year limited warranty, the Charge 6 is your reliable companion for a healthier, more active you.</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1462</v>
+      </c>
+      <c r="H12" t="n">
+        <v>196</v>
+      </c>
+      <c r="I12" t="n">
+        <v>120</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1.668e-05</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Stay on top of your health and fitness goals with the Fitbit Charge 6."</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are evident; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, focusing on product features without exaggeration, such as "the Charge 6 is your reliable companion for a healthier, more active you."</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>The description contains 93 words, which falls in the 91‑110 word range.</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>All claims match the source data: "built-in GPS", "heart‑rate monitor", "up to 7 days of battery life", "aluminum tracker", "multiple color options", and "1‑year limited warranty".</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GoPro HERO12 Black</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>features: 5.3K60 video, HyperSmooth 6.0, waterproof 10 m; capacity: large</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rugged polycarbonate</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Capture your adventures in stunning 5.3K60 video with the GoPro HERO12 Black.  This rugged, waterproof camera features the latest HyperSmooth 6.0 stabilization for unbelievably smooth footage, even in the most action-packed moments. Built to withstand the elements with a durable polycarbonate shell, the HERO12 Black is ready for anything. Plus, its large capacity ensures you can record all your epic memories. Backed by a 1-year limited warranty, you can explore with confidence.</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1393</v>
+      </c>
+      <c r="H13" t="n">
+        <v>203</v>
+      </c>
+      <c r="I13" t="n">
+        <v>107</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1.572e-05</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>The sentence “Capture your adventures in stunning 5.3K60 video with the GoPro HERO12 Black.” reads smoothly without awkward or repetitive phrasing.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>All punctuation and word forms are correct, e.g., “Backed by a 1-year limited warranty, you can explore with confidence.”</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>The description is product‑focused and persuasive, but phrases like “unbelievably smooth footage” add a mild hype that keeps it from being strictly neutral.</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>The description contains 72 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>The claim “waterproof camera” aligns with the waterproof 10 m attribute, and “large capacity ensures you can record all your epic memories” matches the “large” capacity attribute; no unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DJI Mini 4 Pro Drone</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>features: 4K/60fps, omnidirectional obstacle sensing, &lt;250 g; rating: 4.7/5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>composite plastic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Capture stunning 4K footage at 60fps with the DJI Mini 4 Pro! This lightweight drone, weighing under 250g, is perfect for adventurers and beginners alike.  Omnidirectional obstacle sensing keeps you safe, while the durable composite plastic construction ensures lasting performance. Backed by a 1-year limited warranty, the Mini 4 Pro is ready to elevate your aerial photography.</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1164</v>
+      </c>
+      <c r="H14" t="n">
+        <v>207</v>
+      </c>
+      <c r="I14" t="n">
+        <v>88</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1.413e-05</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Capture stunning 4K footage at 60fps with the DJI Mini 4 Pro!” with no awkward or repetitive phrasing.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>No grammar, spelling, or punctuation errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, focusing on product features without exaggerated hype, such as “perfect for adventurers and beginners alike.”</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>The description contains 58 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “4K footage at 60fps,” “omnidirectional obstacle sensing,” “weighing under 250g,” “composite plastic construction,” and “1‑year limited warranty.”</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nintendo Switch OLED</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>features: 7″ OLED screen, docked &amp; handheld modes, 64 GB storage; capacity: large</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>plastic chassis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Experience gaming like never before with the Nintendo Switch OLED!  Its vibrant 7" OLED screen brings your games to life with stunning colors and detail, whether you're playing in handheld or docked mode.  With 64GB of storage, you'll have plenty of room for your favorite Nintendo Switch games.  The durable plastic chassis ensures your console is built to last, backed by a 1-year limited warranty for peace of mind.</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1453</v>
+      </c>
+      <c r="H15" t="n">
+        <v>196</v>
+      </c>
+      <c r="I15" t="n">
+        <v>95</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>1.443e-05</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Experience gaming like never before with the Nintendo Switch OLED! Its vibrant 7" OLED screen brings your games to life..."</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are evident, such as the correct use of "its" and "you’ll have plenty of room".</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, but phrases like “like never before” are slightly overhyped, making it only modestly persuasive.</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>The description contains 69 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>All concrete claims match the product data: "7" OLED screen", "docked &amp; handheld mode", "64GB storage", "plastic chassis", and "1‑year limited warranty" are directly supported.</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PlayStation 5 Slim</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>features: ray tracing, haptic feedback controller, 1 TB SSD; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>plastic shell</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Experience the future of gaming with the PlayStation 5 Slim. Immerse yourself in stunning visuals with ray tracing technology and feel every detail with the innovative haptic feedback controller.  Boasting a spacious 1TB SSD, you'll enjoy lightning-fast load times.  The PlayStation 5 Slim's sleek plastic shell and long-lasting battery make it the perfect companion for your gaming adventures. Backed by a 1-year limited warranty, you can game with confidence.</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1355</v>
+      </c>
+      <c r="H16" t="n">
+        <v>195</v>
+      </c>
+      <c r="I16" t="n">
+        <v>101</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>1.494e-05</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Immerse yourself in stunning visuals with ray tracing technology and feel every detail with the innovative haptic feedback controller.”</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present, such as the correct use of “1‑year limited warranty”.</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, focusing on product features without exaggeration, e.g., “Backed by a 1‑year limited warranty, you can game with confidence.”</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>The description contains 67 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “ray tracing technology”, “haptic feedback controller”, “1TB SSD”, “plastic shell”, “long‑lasting battery”, and “1‑year limited warranty”.</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Xbox Series X</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>features: 12 TFLOPS GPU, 1 TB SSD, 4K @ 120 Hz; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>matte black casing</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Experience next-gen gaming with the powerful Xbox Series X.  Boasting a 12 TFLOPS GPU and a blazing-fast 1TB SSD, this console delivers stunning 4K visuals at up to 120Hz for incredibly smooth gameplay.  Crafted with a sleek matte black casing, the Xbox Series X is as stylish as it is powerful. Enjoy long-lasting battery life and peace of mind with a 1-year limited warranty.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H17" t="n">
+        <v>207</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>1.521e-05</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Experience next-gen gaming with the powerful Xbox Series X" flows naturally without awkward phrasing.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, highlighting features without exaggerated hype, such as "stunning 4K visuals at up to 120Hz for incredibly smooth gameplay".</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>The description contains 64 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: "12 TFLOPS GPU", "1TB SSD", "4K @ 120Hz", "matte black casing", "long‑lasting battery" and "1‑year limited warranty".</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Instant Pot Duo 6‑Quart</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>features: 7‑in‑1 multicooker, stainless steel inner pot, 1000 W heating; weight: light</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>18/8 stainless steel</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The Instant Pot Duo 6-Quart is your kitchen's new best friend! This versatile 7-in-1 multicooker lets you pressure cook, slow cook, sauté, steam, warm, and more, all in one convenient appliance.  Crafted with durable 18/8 stainless steel, including a convenient inner pot, the Duo 6-Quart is built to last.  Plus, with its 1000W heating element, you'll enjoy fast and efficient cooking.  Backed by a 1-year limited warranty, the Instant Pot Duo 6-Quart is a smart choice for busy cooks who want delicious results with ease</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1669</v>
+      </c>
+      <c r="H18" t="n">
+        <v>212</v>
+      </c>
+      <c r="I18" t="n">
+        <v>140</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1.896e-05</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "This versatile 7-in-1 multicooker lets you pressure cook, slow cook, sauté, steam, warm, and more, all in one convenient appliance."</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>No punctuation or spelling errors are evident, such as the correct use of commas and apostrophes throughout the text.</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, but phrases like "new best friend!" add a slight hype element.</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>The description contains 85 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>All claims are supported by the data: "7‑in‑1 multicooker" (features), "18/8 stainless steel" (material), "1000W heating element" (features), and "1‑year limited warranty" (warranty).</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Keurig K‑Supreme Plus Smart</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>features: multistream extraction, BrewID, 78 oz reservoir; capacity: large</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>brushed stainless steel accents</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Elevate your coffee routine with the Keurig K-Supreme Plus Smart.  This sleek brewer, featuring brushed stainless steel accents, boasts a large 78 oz reservoir for endless cups.  Enjoy perfectly brewed coffee thanks to multistream extraction technology and the innovative BrewID system that recognizes your K-Cup pod for optimal flavor. Backed by a 1-year limited warranty, the K-Supreme Plus Smart is your smart choice for delicious coffee at home.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1158</v>
+      </c>
+      <c r="H19" t="n">
+        <v>198</v>
+      </c>
+      <c r="I19" t="n">
+        <v>98</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>1.476e-05</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Elevate your coffee routine with the Keurig K‑Supreme Plus Smart."</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>No punctuation or spelling errors are evident, such as the correct use of “1‑year limited warranty”.</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>The language is friendly and product‑focused without exaggerated hype, e.g., “your smart choice for delicious coffee at home.”</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>The description contains 68 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “multistream extraction”, “BrewID”, “78 oz reservoir”, “brushed stainless steel accents”, and “1‑year limited warranty”.</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Vitamix 5200 Blender</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>features: variable speed, 2‑hp motor, self‑cleaning; sustainably sourced</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BPA‑free Tritan jar</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7‑year warranty</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Experience the power of the Vitamix 5200 Blender!  This kitchen essential boasts a robust 2-hp motor and variable speed control for achieving perfect results, whether you're blending smoothies, soups, or nut butters.  Enjoy peace of mind with the self-cleaning function and a durable, BPA-free Tritan jar.  Plus, rest assured knowing your Vitamix 5200 is backed by a generous 7-year warranty.  Made with sustainability in mind, this blender is a smart choice for your healthy lifestyle.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1456</v>
+      </c>
+      <c r="H20" t="n">
+        <v>199</v>
+      </c>
+      <c r="I20" t="n">
+        <v>120</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>1.677e-05</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Experience the power of the Vitamix 5200 Blender!  This kitchen essential boasts a robust 2-hp motor and variable speed control for achieving perfect results..."</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>No noticeable errors; punctuation and spelling are correct, such as "Enjoy peace of mind with the self-cleaning function and a durable, BPA-free Tritan jar."</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, focusing on product features without exaggerated hype, e.g., "rest assured knowing your Vitamix 5200 is backed by a generous 7-year warranty."</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>The description contains 75 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>All claims match the product data: variable speed, 2‑hp motor, self‑cleaning, BPA‑free Tritan jar, 7‑year warranty, and sustainability are all present and accurately described.</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dyson V15 Detect Vacuum</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>features: laser dust detection, HEPA filtration, 60‑min run‑time; energy efficient</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>polycarbonate &amp; aluminum</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2‑year parts &amp; labor</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Unleash the power of precision cleaning with the Dyson V15 Detect.  See dust you never knew existed with laser dust detection, then breathe easy knowing HEPA filtration captures it all.  Enjoy up to 60 minutes of fade-free suction on a single charge, making cleaning your entire home a breeze.  Crafted from durable polycarbonate and aluminum, the V15 Detect is built to last, backed by a 2-year warranty for your peace of mind.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1271</v>
+      </c>
+      <c r="H21" t="n">
+        <v>198</v>
+      </c>
+      <c r="I21" t="n">
+        <v>101</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>1.503e-05</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Unleash the power of precision cleaning with the Dyson V15 Detect.”</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>There are no noticeable spelling, punctuation, or agreement errors; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>The language is promotional (“Unleash the power…”) and leans toward hype rather than a neutral, factual tone.</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>The description contains 72 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>The claim “fade‑free suction” is not present in the provided product data, which only lists laser dust detection, HEPA filtration, and 60‑min run‑time.</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>iRobot Roomba j7+</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>features: PrecisionVision navigation, self‑emptying Clean Base, Alexa; award‑winning design</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>plastic housing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Meet the iRobot Roomba j7+, the award-winning robot vacuum that takes the hassle out of cleaning.  Equipped with PrecisionVision navigation, it intelligently maps your home and avoids obstacles, leaving no spot untouched.  Enjoy weeks of clean floors thanks to the self-emptying Clean Base, and control it all with your voice using Alexa.  The Roomba j7+ is designed with a durable plastic housing and comes with a 1-year limited warranty for peace of mind.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1273</v>
+      </c>
+      <c r="H22" t="n">
+        <v>196</v>
+      </c>
+      <c r="I22" t="n">
+        <v>103</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>1.515e-05</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Meet the iRobot Roomba j7+, the award-winning robot vacuum that takes the hassle out of cleaning."</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present, such as the correct use of commas and hyphens throughout.</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without exaggerated hype, e.g., "Enjoy weeks of clean floors thanks to the self-emptying Clean Base."</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>The description contains 73 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>All claims match the source data: "PrecisionVision navigation," "self‑emptying Clean Base," "Alexa," "plastic housing," and "1‑year limited warranty" are directly supported.</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Yeti Rambler 20 oz Tumbler</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>features: double‑wall vacuum insulated, MagSlider lid; dimensions: compact</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>kitchen‑grade stainless steel</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5‑year warranty</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Keep your drinks icy cold or piping hot for hours with the Yeti Rambler 20 oz Tumbler.  This compact, double-wall vacuum insulated tumbler is built tough with kitchen-grade stainless steel and features a convenient MagSlider lid.  Enjoy worry-free sipping knowing your Rambler is backed by Yeti's legendary 5-year warranty.</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1008</v>
+      </c>
+      <c r="H23" t="n">
+        <v>197</v>
+      </c>
+      <c r="I23" t="n">
+        <v>76</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>1.275e-05</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>The sentence “Enjoy worry-free sipping knowing your Rambler is backed by Yeti's legendary 5-year warranty.” flows naturally without awkwardness.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>The description contains no spelling, punctuation, or agreement errors, e.g., “double‑wall vacuum insulated tumbler” is correct.</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>The copy is product‑focused, credible, and persuasive without exaggerated hype, such as “built tough with kitchen-grade stainless steel.”</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Word count is 49 words, which falls in the 40‑49 word range.</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>The claim “double‑wall vacuum insulated tumbler” matches the feature list, and the “MagSlider lid” and “5‑year warranty” are directly stated in the source data.</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Stanley Quencher H2.0 40 oz</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>features: vacuum insulated, flow‑state lid, cup‑holder friendly; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>recycled stainless steel</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>lifetime warranty</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stay refreshed all day long with the Stanley Quencher H2.0 40oz! This durable, vacuum-insulated tumbler keeps your drinks cold for hours thanks to its long-lasting battery and recycled stainless steel construction.  The flow-state lid makes sipping easy, and it's cup-holder friendly for on-the-go convenience. Plus, it's backed by a lifetime warranty, so you can enjoy it for years to come.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1522</v>
+      </c>
+      <c r="H24" t="n">
+        <v>200</v>
+      </c>
+      <c r="I24" t="n">
+        <v>98</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>1.482e-05</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Stay refreshed all day long with the Stanley Quencher H2.0 40oz! This durable, vacuum‑insulated tumbler keeps your drinks cold for hours…”.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>No punctuation, spelling, or agreement errors are present, such as the correct phrase “vacuum‑insulated tumbler keeps your drinks cold”.</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>The copy is promotional but stays factual, e.g., “backed by a lifetime warranty”, without exaggerated hype.</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>The description contains 60 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “vacuum‑insulated”, “flow‑state lid”, “cup‑holder friendly”, “long‑lasting battery”, “recycled stainless steel”, and “lifetime warranty”.</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Hydro Flask 32 oz Wide Mouth</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>features: TempShield insulation, Color Last powder coat; dimensions: compact</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pro‑grade stainless steel</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>lifetime warranty</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stay refreshed all day long with the Hydro Flask 32 oz Wide Mouth!  This compact bottle is crafted from durable, pro-grade stainless steel and features TempShield insulation to keep your drinks ice cold or piping hot for hours. The Color Last powder coat ensures your Hydro Flask looks as good as new, no matter where your adventures take you. Plus, it's backed by a lifetime warranty, so you can enjoy worry-free hydration for years to come.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H25" t="n">
+        <v>192</v>
+      </c>
+      <c r="I25" t="n">
+        <v>99</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>1.467e-05</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Stay refreshed all day long with the Hydro Flask 32 oz Wide Mouth!  This compact bottle is crafted…”.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>No noticeable spelling, punctuation, or grammatical errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, highlighting features without exaggeration, such as “backed by a lifetime warranty, so you can enjoy worry‑free hydration”.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>The description contains 75 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “compact bottle”, “pro‑grade stainless steel”, “TempShield insulation”, “Color Last powder coat”, and “lifetime warranty”. No unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Contigo Autoseal West Loop 16 oz</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>features: autoseal spill‑proof lid, double‑wall insulation; dimensions: compact</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>stainless steel</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>lifetime warranty</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stay hydrated on the go with the Contigo Autoseal West Loop! This compact, stainless steel bottle features an Autoseal spill-proof lid for worry-free convenience. Double-wall insulation keeps your drinks hot or cold for hours, making it the perfect companion for your busy day. Plus, enjoy peace of mind with Contigo's lifetime warranty.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1010</v>
+      </c>
+      <c r="H26" t="n">
+        <v>194</v>
+      </c>
+      <c r="I26" t="n">
+        <v>75</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>1.257e-05</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Stay hydrated on the go with the Contigo Autoseal West Loop!” with no awkward or repetitive phrasing.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>All sentences are correctly punctuated and spelled, such as “Double-wall insulation keeps your drinks hot or cold for hours,” which contains no errors.</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, offering a persuasive yet factual pitch without exaggerated hype.</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>The description contains 52 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>The claim “compact, stainless steel bottle features an Autoseal spill‑proof lid” directly matches the product’s material, features, and dimensions, and the “lifetime warranty” aligns with the provided warranty.</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Pegasus 40</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>features: React foam, Zoom Air units, engineered mesh upper; energy efficient</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>textile &amp; synthetic</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2‑year manufacturer warranty</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Experience effortless strides with the Nike Air Zoom Pegasus 40. This energy-efficient running shoe features responsive React foam cushioning and Zoom Air units for a springy, comfortable ride. The breathable engineered mesh upper keeps your feet cool and supported, mile after mile. Backed by a 2-year manufacturer warranty, the Pegasus 40 is ready to take you further.</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1081</v>
+      </c>
+      <c r="H27" t="n">
+        <v>193</v>
+      </c>
+      <c r="I27" t="n">
+        <v>79</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>The description reads naturally, e.g., “Experience effortless strides with the Nike Air Zoom Pegasus 40.”</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or grammatical errors; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>The copy is friendly and product‑focused, using persuasive but not exaggerated language such as “effortless strides” and “ready to take you further.”</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>The description contains 57 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>All claims match the provided data: it mentions “React foam cushioning and Zoom Air units,” “engineered mesh upper,” and “energy‑efficient” as specified, and correctly cites the “2‑year manufacturer warranty.”</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Adidas Ultraboost Light</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>features: Light BOOST midsole, Primeknit+ upper, Continental rubber; rating: 4.7/5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>textile &amp; synthetic</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2‑year manufacturer warranty</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Experience the ultimate in lightweight comfort with the Adidas Ultraboost Light.  These shoes feature a responsive Light BOOST midsole for a springy feel with every step, wrapped in a breathable Primeknit+ upper for a snug, supportive fit.  The Continental rubber outsole provides superior grip on a variety of surfaces. Backed by a 2-year manufacturer warranty, the Ultraboost Light is ready to elevate your performance and comfort.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1079</v>
+      </c>
+      <c r="H28" t="n">
+        <v>199</v>
+      </c>
+      <c r="I28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>1.407e-05</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Experience the ultimate in lightweight comfort with the Adidas Ultraboost Light.”</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or grammatical errors, such as the correct use of “2‑year manufacturer warranty”.</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without exaggeration, e.g., “ready to elevate your performance and comfort.”</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>The description contains 66 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “Light BOOST midsole”, “Primeknit+ upper”, “Continental rubber”, and “2‑year manufacturer warranty”.</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>The North Face ThermoBall Eco Jacket</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>features: synthetic ThermoBall insulation, DWR finish; dimensions: compact</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>100% recycled nylon</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>lifetime warranty</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stay warm and sustainable with The North Face ThermoBall Eco Jacket!  This jacket features cozy ThermoBall synthetic insulation for excellent warmth, even in wet conditions thanks to its DWR finish. Crafted from 100% recycled nylon, it's a compact and eco-friendly choice for your next adventure. Plus, it's backed by The North Face's lifetime warranty, so you can enjoy it for years to come.</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H29" t="n">
+        <v>192</v>
+      </c>
+      <c r="I29" t="n">
+        <v>91</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>1.395e-05</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Stay warm and sustainable with The North Face ThermoBall Eco Jacket!” with no awkward phrasing.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or grammatical errors in the sentence “Crafted from 100% recycled nylon, it's a compact and eco-friendly choice for your next adventure.”</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, highlighting features without exaggerated hype, such as “backed by The North Face's lifetime warranty, so you can enjoy it for years to come.”</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>The description contains 63 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “synthetic ThermoBall insulation,” “DWR finish,” “100% recycled nylon,” “compact,” and “lifetime warranty.”</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Patagonia Black Hole 32 L Backpack</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>features: weather‑resistant, laptop sleeve, padded straps; capacity: large</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>100% recycled polyester ripstop</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>lifetime warranty</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Built to last, the Patagonia Black Hole 32L Backpack is your go-to for everyday adventures. Made from durable, 100% recycled polyester ripstop, this weather-resistant pack is ready for anything.  A spacious interior comfortably holds all your essentials, plus a dedicated laptop sleeve keeps your tech safe.  Padded straps ensure a comfortable carry, no matter how much you pack. Backed by Patagonia's legendary lifetime warranty, this backpack is an investment you can trust.</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2870</v>
+      </c>
+      <c r="H30" t="n">
+        <v>197</v>
+      </c>
+      <c r="I30" t="n">
+        <v>105</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>1.536e-05</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>The sentence “Built to last, the Patagonia Black Hole 32L Backpack is your go‑to for everyday adventures.” flows naturally without awkward phrasing.</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>All punctuation and word forms are correct, e.g., “Made from durable, 100% recycled polyester ripstop, this weather‑resistant pack is ready for anything.”</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>The description is product‑focused, credible and persuasive without hype, such as “Backed by Patagonia's legendary lifetime warranty, this backpack is an investment you can trust.”</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>The description contains 72 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>The claim “weather‑resistant pack” matches the feature “weather‑resistant”, and “dedicated laptop sleeve” matches the feature “laptop sleeve”. All material, capacity, and warranty statements are directly supported by the product data.</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Osprey Farpoint 40</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>features: stowaway harness, laptop sleeve, carry‑on size; energy efficient</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>450D recycled nylon</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>lifetime warranty</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>The Osprey Farpoint 40 is the perfect travel companion. This carry-on sized backpack is crafted from durable 450D recycled nylon and features a stowaway harness for easy airport navigation.  Keep your essentials organized with a dedicated laptop sleeve and enjoy peace of mind with Osprey's lifetime warranty.  Travel light and travel smart with the Farpoint 40.</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="H31" t="n">
+        <v>194</v>
+      </c>
+      <c r="I31" t="n">
+        <v>82</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>1.32e-05</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “This carry-on sized backpack is crafted from durable 450D recycled nylon and features a stowaway harness for easy airport navigation.”</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>No punctuation, spelling, or agreement errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>The language is friendly and product‑focused without exaggerated hype, such as “Travel light and travel smart with the Farpoint 40.”</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>The description contains 56 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “crafted from durable 450D recycled nylon,” “features a stowaway harness,” “dedicated laptop sleeve,” and “lifetime warranty” are directly supported.</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LEGO Star Wars Millennium Falcon 75192</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>features: 7 541 pieces, detailed interior, minifigs included; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ABS plastic bricks</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>lifetime replacement of missing bricks</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Embark on an epic LEGO adventure with the Millennium Falcon 75192! This incredible set boasts 7,541 pieces, allowing you to build a detailed replica of Han Solo's iconic ship.  Explore the intricately designed interior and bring the Star Wars universe to life with the included minifigures.  Built with durable ABS plastic bricks and backed by a lifetime guarantee for missing pieces, this set is a must-have for any Star Wars fan.</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2386</v>
+      </c>
+      <c r="H32" t="n">
+        <v>203</v>
+      </c>
+      <c r="I32" t="n">
+        <v>101</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>1.518e-05</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Embark on an epic LEGO adventure with the Millennium Falcon 75192!" with no awkward or repetitive phrasing.</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or grammatical errors; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, highlighting features without exaggerated hype, such as “must‑have for any Star Wars fan.”</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>The description contains 71 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>All claims are directly supported by the data: "7,541 pieces," "detailed interior," "minifigures included," "ABS plastic bricks," and "lifetime guarantee for missing pieces" match the provided attributes.</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LEGO Icons Botanical Orchid 10311</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>features: 608 pieces, adjustable blooms, decorative set; color options: multiple</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ABS plastic bricks</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>lifetime replacement of missing bricks</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bring a touch of nature indoors with the LEGO Icons Botanical Orchid (10311). This stunning set features 608 pieces that assemble into a beautiful, lifelike orchid with adjustable blooms.  Display this decorative piece in your home and enjoy the satisfaction of building a unique and elegant model. Crafted from high-quality ABS plastic bricks, this set comes with a lifetime guarantee for missing bricks, ensuring your orchid blooms forever.</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>896</v>
+      </c>
+      <c r="H33" t="n">
+        <v>198</v>
+      </c>
+      <c r="I33" t="n">
+        <v>91</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>1.413e-05</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Bring a touch of nature indoors with the LEGO Icons Botanical Orchid (10311).”</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present, such as “Crafted from high-quality ABS plastic bricks, this set comes with a lifetime guarantee.”</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without hype, e.g., “Display this decorative piece in your home and enjoy the satisfaction of building a unique and elegant model.”</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>The description contains 68 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “608 pieces,” “adjustable blooms,” “decorative set,” “ABS plastic bricks,” and “lifetime guarantee for missing bricks.”</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kindle Paperwhite 11th Gen</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>features: 6.8″ glare‑free display, 10‑week battery, USB‑C; dimensions: compact</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>recycled plastic</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Escape into a world of endless reading with the Kindle Paperwhite 11th Gen. Its spacious 6.8" glare-free display makes every page a joy to read, whether you're lounging by the pool or curled up on the couch.  Enjoy weeks of reading on a single charge with the impressive 10-week battery life, and conveniently power up with the included USB-C cable.  This compact device is crafted with recycled plastic, making it a sustainable choice for book lovers everywhere.  Backed by a 1-year limited warranty, the Kindle Paperwhite is ready to become your new reading companion.</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1531</v>
+      </c>
+      <c r="H34" t="n">
+        <v>204</v>
+      </c>
+      <c r="I34" t="n">
+        <v>134</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>1.818e-05</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>The description reads naturally, e.g., “Escape into a world of endless reading with the Kindle Paperwhite 11th Gen.”</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or agreement errors; the sentence “Enjoy weeks of reading on a single charge with the impressive 10-week battery life” is correct.</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>The copy is friendly and persuasive without hype, as shown by the phrase “a sustainable choice for book lovers everywhere.”</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>The description contains 92 words, which falls in the 91‑110 word range.</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>All claims match the data: “6.8" glare‑free display,” “10‑week battery life,” “USB‑C,” “crafted with recycled plastic,” and “1‑year limited warranty.” No unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kobo Libra 2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>features: 7″ E Ink Carta, Bluetooth audiobooks, waterproof IPX8; weight: light</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>plastic chassis</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dive into a world of reading with the Kobo Libra 2.  Its stunning 7″ E Ink Carta display delivers a crisp, paper-like reading experience, perfect for hours of enjoyment.  Listen to your favorite audiobooks wirelessly with Bluetooth, and never worry about a spilled drink thanks to its IPX8 waterproof rating.  Lightweight and designed with a durable plastic chassis, the Libra 2 is your perfect reading companion, backed by a 1-year limited warranty.</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2957</v>
+      </c>
+      <c r="H35" t="n">
+        <v>195</v>
+      </c>
+      <c r="I35" t="n">
+        <v>101</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>1.494e-05</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Dive into a world of reading with the Kobo Libra 2."</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>No punctuation or spelling errors are evident, e.g., "Listen to your favorite audiobooks wirelessly with Bluetooth, and never worry about a spilled drink..."</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without hype, such as "the Libra 2 is your perfect reading companion."</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>The description contains 72 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>All claims match the source: "7″ E Ink Carta display," "Bluetooth," "IPX8 waterproof rating," "lightweight," "plastic chassis," and "1‑year limited warranty" are directly supported by the product data.</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Anker Soundcore Motion+ Speaker</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>features: 30 W audio, Hi‑Res, IPX7 waterproof; energy efficient</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>aluminum grille</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>18‑month warranty</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Experience powerful, crystal-clear audio with the Anker Soundcore Motion+ Speaker. This sleek aluminum grille speaker delivers 30W of Hi-Res sound, perfect for immersing yourself in your favorite music.  Enjoy worry-free listening with its IPX7 waterproof rating, making it ideal for any adventure. Plus, the Motion+ is energy efficient, so you can listen longer without draining your battery. Backed by an 18-month warranty, you can be confident in your purchase.</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1044</v>
+      </c>
+      <c r="H36" t="n">
+        <v>195</v>
+      </c>
+      <c r="I36" t="n">
+        <v>104</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>1.521e-05</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Experience powerful, crystal-clear audio with the Anker Soundcore Motion+ Speaker."</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>No punctuation or spelling errors are evident, such as the correct use of commas and hyphens throughout the text.</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>The language is friendly and product‑focused without exaggerated hype, e.g., "Backed by an 18-month warranty, you can be confident in your purchase."</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>The description contains 69 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: "30W of Hi‑Res sound," "IPX7 waterproof rating," "aluminum grille speaker," "energy efficient," and "18‑month warranty" are directly supported.</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sonos Move 2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>features: WiFi &amp; Bluetooth, 24‑hr battery, automatic Trueplay; rating: 4.7/5</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>shock‑resistant shell</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The Sonos Move 2 is your ultimate portable sound companion.  Stream effortlessly via WiFi or Bluetooth, and enjoy up to 24 hours of playtime on a single charge.  Automatic Trueplay tuning ensures your music always sounds its best, wherever you are.  Crafted with a durable, shock-resistant shell, the Move 2 is built to keep up with your adventures. Backed by a 1-year limited warranty, experience exceptional sound quality and freedom with the Sonos Move 2.</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1087</v>
+      </c>
+      <c r="H37" t="n">
+        <v>201</v>
+      </c>
+      <c r="I37" t="n">
+        <v>105</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>1.548e-05</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Stream effortlessly via WiFi or Bluetooth, and enjoy up to 24 hours of playtime on a single charge.”</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>No punctuation, spelling, or agreement errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>The language is friendly and product‑focused without exaggerated hype, such as “your ultimate portable sound companion.”</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>The description contains 74 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “WiFi or Bluetooth,” “up to 24 hours of playtime,” “Automatic Trueplay,” “shock‑resistant shell,” and “1‑year limited warranty.” No unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Philips Hue White &amp; Color Ambiance Starter Kit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>features: 16 million colors, Bluetooth &amp; Zigbee, voice control; limited edition</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>plastic bulbs</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Unleash a world of color and ambiance with the Philips Hue White &amp; Color Ambiance Starter Kit! This limited-edition kit features three smart bulbs that offer 16 million vibrant colors and warm white tones to transform your space. Control your lights effortlessly with Bluetooth or Zigbee connectivity, and use your voice with compatible assistants for ultimate convenience.  Backed by a 2-year limited warranty, experience the magic of smart lighting.</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>896</v>
+      </c>
+      <c r="H38" t="n">
+        <v>198</v>
+      </c>
+      <c r="I38" t="n">
+        <v>92</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>1.422e-05</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>The sentence "Backed by a 2-year limited warranty, experience the magic of smart lighting." is slightly abrupt, making the flow a bit jarring.</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable spelling, punctuation, or grammatical errors.</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Phrases like "Unleash a world of color" and "experience the magic" are overly promotional, giving a slightly overhyped tone.</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>The description contains 69 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>The text mentions "three smart bulbs" and "warm white tones," which are not specified in the provided product data; these are inferred details rather than directly supported.</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TP‑Link Deco XE75 Mesh WiFi 6E</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>features: tri‑band AXE5400, 3‑pack covers 7 200 sq ft; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Experience seamless, lightning-fast WiFi throughout your entire home with the TP-Link Deco XE75 Mesh WiFi 6E 3-pack. This powerful system delivers tri-band AXE5400 speeds, covering up to 7,200 square feet. Enjoy long-lasting battery life and reliable performance with this durable plastic construction. Backed by a 2-year limited warranty, the Deco XE75 is your solution for a truly connected home.</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1022</v>
+      </c>
+      <c r="H39" t="n">
+        <v>214</v>
+      </c>
+      <c r="I39" t="n">
+        <v>101</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>1.551e-05</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>The sentence flows naturally, e.g., “Experience seamless, lightning-fast WiFi throughout your entire home…”.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>No spelling or punctuation errors are present; the text is grammatically correct.</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>The description is promotional but stays within a reasonable, product‑focused tone without exaggerated hype.</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>The description contains 58 words, which is within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>The claim “Enjoy long‑lasting battery life” is not supported by the provided attributes (only a generic “long‑lasting” battery note is given, but the product is a Wi‑Fi router with no battery).</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Eufy Video Doorbell Dual</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>features: dual camera, package detection, 2K resolution; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>plastic housing</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Keep an eye on your home with the Eufy Video Doorbell Dual. This innovative doorbell features dual cameras, giving you a wider field of view to see everything happening at your doorstep. With 2K resolution, you'll get crystal-clear images, even at night. Plus, the package detection feature alerts you when a package arrives, so you can keep track of your deliveries.  Enjoy long-lasting battery life and peace of mind with the Eufy Video Doorbell Dual, backed by a 1-year limited warranty.</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1311</v>
+      </c>
+      <c r="H40" t="n">
+        <v>195</v>
+      </c>
+      <c r="I40" t="n">
+        <v>114</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>1.611e-05</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Keep an eye on your home with the Eufy Video Doorbell Dual.”</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>There are no noticeable errors; punctuation and spelling are correct throughout the text.</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without exaggerated hype, such as “Enjoy long‑lasting battery life and peace of mind.”</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>The description contains 81 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>All concrete claims—dual cameras, package detection, 2K resolution, long‑lasting battery, and 1‑year limited warranty—match the provided attributes; no unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Blink Outdoor 4</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>features: 1080p HD, 2‑year battery, weather‑resistant; limited edition</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Get crystal-clear security with the Blink Outdoor 4, a limited-edition camera that delivers stunning 1080p HD video.  Powered by a long-lasting 2-year battery, it's weather-resistant and built to withstand the elements. Enjoy peace of mind knowing your home is protected, day and night, with the Blink Outdoor 4. Backed by a 1-year limited warranty.</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>947</v>
+      </c>
+      <c r="H41" t="n">
+        <v>195</v>
+      </c>
+      <c r="I41" t="n">
+        <v>91</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>1.404e-05</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Get crystal-clear security with the Blink Outdoor 4, a limited-edition camera that delivers stunning 1080p HD video."</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>No punctuation, spelling, or agreement errors are present, such as the correct use of "it's weather-resistant and built to withstand the elements."</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>The language is friendly and product‑focused without exaggerated hype, though phrases like "crystal-clear security" are slightly promotional.</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>The description contains 54 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: "1080p HD video," "2‑year battery," "weather‑resistant," "limited‑edition," and "1‑year limited warranty" are directly supported.</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Corsair K100 RGB Keyboard</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>features: Cherry MX Speed, 4000 Hz polling, aluminum frame; capacity: large</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>brushed aluminum</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2‑year warranty</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Experience lightning-fast responsiveness with the Corsair K100 RGB Keyboard. Featuring Cherry MX Speed switches and blazing-fast 4000Hz polling, every keystroke registers instantly.  Crafted with a durable brushed aluminum frame, this large capacity keyboard is built to withstand intense gaming sessions. Backed by a 2-year warranty, the K100 RGB delivers premium performance and reliability.</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1673</v>
+      </c>
+      <c r="H42" t="n">
+        <v>197</v>
+      </c>
+      <c r="I42" t="n">
+        <v>86</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>1.365e-05</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Experience lightning-fast responsiveness with the Corsair K100 RGB Keyboard.”</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present, such as “Crafted with a durable brushed aluminum frame,” which is correct.</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>The tone is product‑focused and credible, highlighting features without exaggerated hype, e.g., “Backed by a 2‑year warranty, the K100 RGB delivers premium performance and reliability.”</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>The description contains 53 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “Cherry MX Speed switches,” “4000Hz polling,” “brushed aluminum frame,” “large capacity,” and “2‑year warranty.”</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Logitech MX Master 3S</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>features: 8K DPI sensor, MagSpeed scroll, Bolt &amp; Bluetooth; color options: multiple</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Experience unparalleled precision and comfort with the Logitech MX Master 3S.  Its 8K DPI sensor delivers smooth, accurate tracking, while the MagSpeed scroll wheel lets you fly through documents with ease.  Connect seamlessly via Bolt or Bluetooth, and choose from multiple colors to match your style.  Backed by a 1-year limited warranty, the MX Master 3S is the perfect choice for productivity on the go.</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>2803</v>
+      </c>
+      <c r="H43" t="n">
+        <v>195</v>
+      </c>
+      <c r="I43" t="n">
+        <v>91</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>1.404e-05</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Connect seamlessly via Bolt or Bluetooth, and choose from multiple colors to match your style.”</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or grammatical errors, such as the correct use of “its 8K DPI sensor delivers smooth, accurate tracking.”</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused but includes a slight hype phrase (“unparalleled precision”), making it a bit generic.</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>The description contains 65 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>All claims are supported by the data: “8K DPI sensor,” “MagSpeed scroll wheel,” “Bolt &amp; Bluetooth,” “multiple colors,” and “1‑year limited warranty.” No unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Razer DeathAdder V3 Pro</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>features: 63 g ultralight, 30K DPI Focus Pro sensor; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2‑year warranty</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dominate the competition with the Razer DeathAdder V3 Pro.  This ultralight gaming mouse, weighing in at just 63g, features the incredibly accurate 30K DPI Focus Pro sensor for pinpoint precision.  Enjoy long-lasting battery life so you can game without interruption. Backed by a 2-year warranty, the DeathAdder V3 Pro is built to last.</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>952</v>
+      </c>
+      <c r="H44" t="n">
+        <v>198</v>
+      </c>
+      <c r="I44" t="n">
+        <v>85</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>1.359e-05</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Dominate the competition with the Razer DeathAdder V3 Pro."</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>No punctuation or spelling errors are present, such as the correct use of commas and hyphens.</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>The copy is enthusiastic but not overly exaggerated, staying product‑focused (e.g., "Enjoy long‑lasting battery life so you can game without interruption").</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>The description contains 53 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>All claims match the source data: "63g" ultralight, "30K DPI Focus Pro sensor", and "long‑lasting battery" are directly supported by the attributes.</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Samsung 980 Pro 2 TB NVMe SSD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>features: PCIe 4.0, up to 7 000 MB/s read, nickel coating; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PCB &amp; NAND flash</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Experience lightning-fast performance with the Samsung 980 Pro 2TB NVMe SSD.  Powered by PCIe 4.0 technology, this drive delivers blazing-fast read speeds of up to 7,000 MB/s, making your applications and files launch in an instant.  The nickel coating helps keep things cool, while the durable PCB and NAND flash construction ensure long-lasting reliability. Backed by a 5-year limited warranty, the Samsung 980 Pro is the perfect choice for demanding users who need the ultimate in speed and performance.</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1132</v>
+      </c>
+      <c r="H45" t="n">
+        <v>214</v>
+      </c>
+      <c r="I45" t="n">
+        <v>122</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>1.74e-05</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Powered by PCIe 4.0 technology, this drive delivers blazing‑fast read speeds of up to 7,000 MB/s, making your applications and files launch in an instant.”</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>No punctuation, spelling, or agreement errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>The copy is product‑focused and persuasive without exaggerated hype, though phrases like “the ultimate in speed and performance” are mildly promotional.</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>The description contains 79 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>All concrete claims—PCIe 4.0, up to 7,000 MB/s read, nickel coating, PCB &amp; NAND flash construction, and a 5‑year limited warranty—are directly supported by the product data.</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Seagate Portable 5 TB HDD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>features: USB 3.0, plug‑and‑play, 2.5″ form factor; rating: 4.7/5</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>plastic shell</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Take your files on the go with the Seagate Portable 5TB HDD. This compact drive, featuring a sleek plastic shell and 2.5" form factor, easily slips into your bag for effortless portability. Simply plug it into any USB 3.0 port and start transferring data instantly with plug-and-play convenience. Backed by a 4.7/5 star rating and a 1-year limited warranty, you can trust this drive for all your storage needs.</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1105</v>
+      </c>
+      <c r="H46" t="n">
+        <v>208</v>
+      </c>
+      <c r="I46" t="n">
+        <v>103</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>1.551e-05</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Take your files on the go with the Seagate Portable 5TB HDD.”</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or agreement errors, such as the correct use of “plug-and-play convenience.”</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without hype, e.g., “you can trust this drive for all your storage needs.”</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>The description contains 69 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “plastic shell” and “2.5" form factor,” “USB 3.0,” “plug‑and‑play,” “4.7/5 star rating,” and “1‑year limited warranty.”</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SanDisk Extreme PRO 128 GB SDXC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>features: UHS‑I U3, 200 MB/s read, waterproof; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>lifetime limited warranty</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Capture every epic moment with the SanDisk Extreme PRO 128GB SDXC card.  This UHS-I U3 card boasts blazing-fast 200MB/s read speeds, ensuring smooth performance for high-resolution photos and 4K video.  Built to withstand the elements, it's waterproof, so you can shoot with confidence wherever your adventures take you.  Backed by a lifetime limited warranty, the SanDisk Extreme PRO is your reliable companion for all your creative endeavors.</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1289</v>
+      </c>
+      <c r="H47" t="n">
+        <v>204</v>
+      </c>
+      <c r="I47" t="n">
+        <v>109</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>1.593e-05</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Capture every epic moment with the SanDisk Extreme PRO 128GB SDXC card.”</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or grammatical errors; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without hype, such as “Backed by a lifetime limited warranty, the SanDisk Extreme PRO is your reliable companion.”</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>The description contains 67 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>All claims match the source data: “UHS‑I U3 card boasts … 200MB/s read speeds,” “it's waterproof,” and “Backed by a lifetime limited warranty.” No unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kingston Fury Beast 32 GB DDR5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>features: 6000 MT/s, Intel XMP 3.0, low‑profile heat spreader; energy efficient</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>aluminum heatspreader</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>lifetime warranty</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Unleash the beast within your system with the Kingston Fury Beast 32GB DDR5.  This high-performance memory boasts a blazing 6000MT/s speed and Intel XMP 3.0 support for effortless overclocking. The low-profile aluminum heat spreader keeps things cool and efficient, while a lifetime warranty ensures lasting reliability. Upgrade your gaming and productivity experience with the Kingston Fury Beast.</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>972</v>
+      </c>
+      <c r="H48" t="n">
+        <v>206</v>
+      </c>
+      <c r="I48" t="n">
+        <v>89</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>1.419e-05</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Unleash the beast within your system with the Kingston Fury Beast 32GB DDR5.”</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>There are no noticeable errors; the sentence structure and punctuation are correct throughout.</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>The phrasing is product‑focused but uses hype‑y language like “Unleash the beast,” which is a mild overstatement.</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>The description contains 58 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>All concrete claims—“6000 MT/s speed,” “Intel XMP 3.0 support,” “low‑profile aluminum heat spreader,” and “lifetime warranty”—are directly supported by the product data.</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Acer Predator XB273U 27″ Monitor</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>features: 2560×1440 170 Hz IPS, HDR400, G‑Sync Compatible; capacity: large</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>plastic &amp; metal stand</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3‑year warranty</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dominate your games with the Acer Predator XB273U 27" Monitor.  Experience stunning visuals with a 2560x1440 resolution, vibrant 170Hz IPS display, and HDR400 for incredible detail and color.  G-Sync Compatible technology ensures buttery-smooth gameplay, eliminating screen tearing and stuttering. Built with a durable plastic and metal stand, this large monitor is backed by a 3-year warranty for peace of mind.</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1088</v>
+      </c>
+      <c r="H49" t="n">
+        <v>216</v>
+      </c>
+      <c r="I49" t="n">
+        <v>105</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>1.593e-05</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Experience stunning visuals with a 2560x1440 resolution, vibrant 170Hz IPS display, and HDR400 for incredible detail and color.”</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>No punctuation, spelling, or agreement errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>The copy is product‑focused and persuasive without exaggerated hype, using a friendly tone such as “Dominate your games with the Acer Predator XB273U 27" Monitor.”</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>The description contains 60 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “2560x1440 resolution, vibrant 170Hz IPS display, HDR400, G‑Sync Compatible… durable plastic and metal stand… 3‑year warranty.”</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BenQ PD2725U 27″ Monitor</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>features: 4K UHD IPS, 98% P3, Thunderbolt 3; color options: multiple</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>metal stand</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3‑year warranty</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Experience breathtaking clarity and vibrant colors with the BenQ PD2725U 27" Monitor.  Its 4K UHD IPS display delivers stunning detail, while 98% P3 coverage ensures accurate and lifelike color reproduction.  Seamlessly connect your devices with Thunderbolt 3 and enjoy the sleek, modern design of the metal stand. Backed by a 3-year warranty, the PD2725U is your perfect companion for creative work and entertainment.</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1022</v>
+      </c>
+      <c r="H50" t="n">
+        <v>205</v>
+      </c>
+      <c r="I50" t="n">
+        <v>105</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>1.56e-05</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Experience breathtaking clarity and vibrant colors with the BenQ PD2725U 27" Monitor.”</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>The text is product‑focused and persuasive but uses a slightly over‑hyped phrase “breathtaking clarity,” making it less than fully neutral.</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>The description contains 63 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>All concrete claims—4K UHD IPS display, 98% P3 coverage, Thunderbolt 3, metal stand, and 3‑year warranty—match the provided product data, with no unsupported features added.</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>ASUS ProArt PA278QV Monitor</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>features: 27″ 2560×1440 IPS, 100% sRGB, Calman Verified; weight: light</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>metal stand</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3‑year warranty</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The ASUS ProArt PA278QV is your gateway to stunning visuals and professional-grade color accuracy.  This 27" monitor boasts a crisp 2560x1440 IPS display, covering 100% of the sRGB color gamut and Calman Verified for exceptional color reproduction.  Its lightweight design and durable metal stand make it perfect for any workspace. Plus, enjoy peace of mind with the included 3-year warranty.</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1015</v>
+      </c>
+      <c r="H51" t="n">
+        <v>211</v>
+      </c>
+      <c r="I51" t="n">
+        <v>101</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>1.542e-05</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "The ASUS ProArt PA278QV is your gateway to stunning visuals and professional‑grade color accuracy."</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>No punctuation, spelling, or agreement errors are present, such as the correct use of "Calman Verified for exceptional color reproduction."</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without hype, e.g., "Plus, enjoy peace of mind with the included 3‑year warranty."</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>The description contains 60 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>All claims match the source: "27" monitor boasts a crisp 2560x1440 IPS display, covering 100% of the sRGB color gamut and Calman Verified" and "lightweight design and durable metal stand" plus the "3‑year warranty".</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Product_attribute_list</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>warranty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>generated_description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>latency_ms</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fluency</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>grammar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>tone</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>grounding</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>latency_rating</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>cost_rating</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>final_score</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>joint_judge_model</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fluency_judge_explanation</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fluency_judge_verdict</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>grammar_judge_explanation</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>grammar_judge_verdict</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>tone_judge_explanation</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>tone_judge_verdict</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>length_judge_explanation</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>length_judge_verdict</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>grounding_judge_explanation</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>grounding_judge_verdict</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>judge_final_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 Pro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>features: A17 Pro chip, 120 Hz ProMotion display, USB‑C fast charging; dimensions: compact</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>titanium frame, Ceramic Shield glass</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Experience the power and elegance of the iPhone 15 Pro.  Fueled by the blazing-fast A17 Pro chip and boasting a stunning 120Hz ProMotion display, this compact powerhouse delivers an unparalleled user experience.  Crafted with a durable titanium frame and protective Ceramic Shield glass, the iPhone 15 Pro is built to last. Plus, enjoy the convenience of USB-C fast charging. Backed by a 1-year limited warranty, the iPhone 15 Pro is the ultimate choice for discerning users.</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1914</v>
+      </c>
+      <c r="H2" t="n">
+        <v>207</v>
+      </c>
+      <c r="I2" t="n">
+        <v>115</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1.656e-05</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Experience the power and elegance of the iPhone 15 Pro."</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>No punctuation or spelling errors are evident, such as the correct hyphenation in "blazing-fast".</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>The language is product‑focused and credible, but phrases like "blazing‑fast" and "ultimate choice" add mild hype.</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>The description contains 76 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: "A17 Pro chip", "120Hz ProMotion display", "compact", "titanium frame", "Ceramic Shield glass", "USB‑C fast charging", and "1‑year limited warranty".</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sony WH‑1000XM5 Headphones</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>features: active noise cancelling, 30 hr battery, Bluetooth 5.2; capacity: large</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>synthetic leather earcups</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Escape into your own world of sound with the Sony WH-1000XM5 Headphones.  These premium headphones boast industry-leading active noise cancelling, so you can focus on your music, podcast, or audiobook without distractions. Enjoy up to 30 hours of battery life on a single charge and seamless Bluetooth 5.2 connectivity.  Crafted with comfortable synthetic leather earcups, the XM5s are perfect for extended listening sessions.  Backed by a 1-year limited warranty, you can experience audio excellence with confidence.</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1410</v>
+      </c>
+      <c r="H3" t="n">
+        <v>204</v>
+      </c>
+      <c r="I3" t="n">
+        <v>115</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1.647e-05</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Escape into your own world of sound with the Sony WH-1000XM5 Headphones."</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>There are no noticeable errors; the sentence "Backed by a 1-year limited warranty, you can experience audio excellence with confidence." is grammatically correct.</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, focusing on product features without exaggeration, such as "industry-leading active noise cancelling" which is a common claim for this model.</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>The description contains 76 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: "active noise cancelling", "30 hours of battery life", "Bluetooth 5.2", "synthetic leather earcups", and "1‑year limited warranty" are directly stated in the description.</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amazon Echo Dot (5th Gen)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>features: Alexa voice assistant, temperature sensor, improved bass; sustainably sourced</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>recycled fabric mesh</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Meet the new Echo Dot, packed with smart features and sustainable style.  
+With Alexa, you can control your smart home, play music, get answers to questions, and more, all with just your voice. This 5th generation Echo Dot boasts an improved bass for richer sound and even includes a temperature sensor for added convenience. Plus, it's crafted with a cozy recycled fabric mesh, making it a responsible choice for your home.  Enjoy peace of mind with a 1-year limited warranty.</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1326</v>
+      </c>
+      <c r="H4" t="n">
+        <v>193</v>
+      </c>
+      <c r="I4" t="n">
+        <v>108</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1.551e-05</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Meet the new Echo Dot, packed with smart features and sustainable style.” No awkward or repetitive phrasing is present.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>There are no noticeable spelling, punctuation, or grammatical errors; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, highlighting features without exaggerated hype, such as “Enjoy peace of mind with a 1‑year limited warranty.”</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>The description contains 79 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “improved bass,” “temperature sensor,” “recycled fabric mesh,” and “1‑year limited warranty” are all directly listed in the attributes.</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fitbit Charge 6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>features: heart‑rate monitor, built‑in GPS, 7‑day battery; color options: multiple</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>aluminum case</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stay on top of your health and fitness goals with the Fitbit Charge 6. This sleek aluminum tracker features a built-in GPS to accurately map your runs and walks, plus a heart-rate monitor to keep tabs on your exertion. Enjoy up to 7 days of battery life on a single charge, so you can focus on your activity, not your charger.  Choose from multiple color options to find the perfect fit for your style.  Backed by a 1-year limited warranty, the Charge 6 is your reliable companion for a healthier, more active you.</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1462</v>
+      </c>
+      <c r="H5" t="n">
+        <v>196</v>
+      </c>
+      <c r="I5" t="n">
+        <v>120</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1.668e-05</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Stay on top of your health and fitness goals with the Fitbit Charge 6."</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are evident; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, focusing on product features without exaggeration, such as "the Charge 6 is your reliable companion for a healthier, more active you."</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>The description contains 93 words, which falls in the 91‑110 word range.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>All claims match the source data: "built-in GPS", "heart‑rate monitor", "up to 7 days of battery life", "aluminum tracker", "multiple color options", and "1‑year limited warranty".</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DJI Mini 4 Pro Drone</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>features: 4K/60fps, omnidirectional obstacle sensing, &lt;250 g; rating: 4.7/5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>composite plastic</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Capture stunning 4K footage at 60fps with the DJI Mini 4 Pro! This lightweight drone, weighing under 250g, is perfect for adventurers and beginners alike.  Omnidirectional obstacle sensing keeps you safe, while the durable composite plastic construction ensures lasting performance. Backed by a 1-year limited warranty, the Mini 4 Pro is ready to elevate your aerial photography.</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1164</v>
+      </c>
+      <c r="H6" t="n">
+        <v>207</v>
+      </c>
+      <c r="I6" t="n">
+        <v>88</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1.413e-05</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Capture stunning 4K footage at 60fps with the DJI Mini 4 Pro!” with no awkward or repetitive phrasing.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>No grammar, spelling, or punctuation errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>The tone is friendly and credible, focusing on product features without exaggerated hype, such as “perfect for adventurers and beginners alike.”</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>The description contains 58 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: “4K footage at 60fps,” “omnidirectional obstacle sensing,” “weighing under 250g,” “composite plastic construction,” and “1‑year limited warranty.”</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Xbox Series X</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>features: 12 TFLOPS GPU, 1 TB SSD, 4K @ 120 Hz; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>matte black casing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Experience next-gen gaming with the powerful Xbox Series X.  Boasting a 12 TFLOPS GPU and a blazing-fast 1TB SSD, this console delivers stunning 4K visuals at up to 120Hz for incredibly smooth gameplay.  Crafted with a sleek matte black casing, the Xbox Series X is as stylish as it is powerful. Enjoy long-lasting battery life and peace of mind with a 1-year limited warranty.</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>207</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1.521e-05</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Experience next-gen gaming with the powerful Xbox Series X" flows naturally without awkward phrasing.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>No spelling, punctuation, or grammatical errors are present; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, highlighting features without exaggerated hype, such as "stunning 4K visuals at up to 120Hz for incredibly smooth gameplay".</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>The description contains 64 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>All concrete claims match the source data: "12 TFLOPS GPU", "1TB SSD", "4K @ 120Hz", "matte black casing", "long‑lasting battery" and "1‑year limited warranty".</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Instant Pot Duo 6‑Quart</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>features: 7‑in‑1 multicooker, stainless steel inner pot, 1000 W heating; weight: light</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>18/8 stainless steel</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The Instant Pot Duo 6-Quart is your kitchen's new best friend! This versatile 7-in-1 multicooker lets you pressure cook, slow cook, sauté, steam, warm, and more, all in one convenient appliance.  Crafted with durable 18/8 stainless steel, including a convenient inner pot, the Duo 6-Quart is built to last.  Plus, with its 1000W heating element, you'll enjoy fast and efficient cooking.  Backed by a 1-year limited warranty, the Instant Pot Duo 6-Quart is a smart choice for busy cooks who want delicious results with ease</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1669</v>
+      </c>
+      <c r="H8" t="n">
+        <v>212</v>
+      </c>
+      <c r="I8" t="n">
+        <v>140</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1.896e-05</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "This versatile 7-in-1 multicooker lets you pressure cook, slow cook, sauté, steam, warm, and more, all in one convenient appliance."</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>No punctuation or spelling errors are evident, such as the correct use of commas and apostrophes throughout the text.</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, but phrases like "new best friend!" add a slight hype element.</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>The description contains 85 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>All claims are supported by the data: "7‑in‑1 multicooker" (features), "18/8 stainless steel" (material), "1000W heating element" (features), and "1‑year limited warranty" (warranty).</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LEGO Star Wars Millennium Falcon 75192</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>features: 7 541 pieces, detailed interior, minifigs included; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ABS plastic bricks</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>lifetime replacement of missing bricks</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Embark on an epic LEGO adventure with the Millennium Falcon 75192! This incredible set boasts 7,541 pieces, allowing you to build a detailed replica of Han Solo's iconic ship.  Explore the intricately designed interior and bring the Star Wars universe to life with the included minifigures.  Built with durable ABS plastic bricks and backed by a lifetime guarantee for missing pieces, this set is a must-have for any Star Wars fan.</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2386</v>
+      </c>
+      <c r="H9" t="n">
+        <v>203</v>
+      </c>
+      <c r="I9" t="n">
+        <v>101</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1.518e-05</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Embark on an epic LEGO adventure with the Millennium Falcon 75192!" with no awkward or repetitive phrasing.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>There are no spelling, punctuation, or grammatical errors; the sentence structure is correct throughout.</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused, highlighting features without exaggerated hype, such as “must‑have for any Star Wars fan.”</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>The description contains 71 words, which falls within the 50‑90 word target range.</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>All claims are directly supported by the data: "7,541 pieces," "detailed interior," "minifigures included," "ABS plastic bricks," and "lifetime guarantee for missing pieces" match the provided attributes.</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Eufy Video Doorbell Dual</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>features: dual camera, package detection, 2K resolution; battery: long‑lasting</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>plastic housing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1‑year limited warranty</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>google/gemma-2-9b-it-fast</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Keep an eye on your home with the Eufy Video Doorbell Dual. This innovative doorbell features dual cameras, giving you a wider field of view to see everything happening at your doorstep. With 2K resolution, you'll get crystal-clear images, even at night. Plus, the package detection feature alerts you when a package arrives, so you can keep track of your deliveries.  Enjoy long-lasting battery life and peace of mind with the Eufy Video Doorbell Dual, backed by a 1-year limited warranty.</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1311</v>
+      </c>
+      <c r="H10" t="n">
+        <v>195</v>
+      </c>
+      <c r="I10" t="n">
+        <v>114</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1.611e-05</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., “Keep an eye on your home with the Eufy Video Doorbell Dual.”</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>There are no noticeable errors; punctuation and spelling are correct throughout the text.</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>The tone is friendly and product‑focused without exaggerated hype, such as “Enjoy long‑lasting battery life and peace of mind.”</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>The description contains 81 words, which falls within the 50‑90 word range.</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>All concrete claims—dual cameras, package detection, 2K resolution, long‑lasting battery, and 1‑year limited warranty—match the provided attributes; no unsupported features are added.</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ASUS ProArt PA278QV Monitor</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>features: 27″ 2560×1440 IPS, 100% sRGB, Calman Verified; weight: light</t>
@@ -1942,17 +8303,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The ASUS ProArt PA278QV is a 27-inch monitor with a stunning 2560x1440 IPS display, delivering vibrant colors with 100% sRGB coverage. Calman Verified for accurate color reproduction, this monitor is perfect for professionals who demand precision.  Its lightweight design and durable metal stand ensure a comfortable and stable viewing experience. Backed by a 3-year warranty, the PA278QV offers peace of mind for your creative endeavors.</t>
+          <t>The ASUS ProArt PA278QV is your gateway to stunning visuals and professional-grade color accuracy.  This 27" monitor boasts a crisp 2560x1440 IPS display, covering 100% of the sRGB color gamut and Calman Verified for exceptional color reproduction.  Its lightweight design and durable metal stand make it perfect for any workspace. Plus, enjoy peace of mind with the included 3-year warranty.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1188</v>
+        <v>1015</v>
       </c>
       <c r="H11" t="n">
-        <v>295</v>
+        <v>211</v>
       </c>
       <c r="I11" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1976,7 +8337,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1986,7 +8347,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1995,72 +8356,1294 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>1.753e-05</v>
+        <v>1.542e-05</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>prompt_engineering</t>
+          <t>openai/gpt-oss-120b-fast</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b-it-fast</t>
+          <t>The description reads smoothly, e.g., "The ASUS ProArt PA278QV is your gateway to stunning visuals and professional‑grade color accuracy."</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>The description reads smoothly and naturally without awkward phrasing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>No punctuation, spelling, or agreement errors are present, such as the correct use of "Calman Verified for exceptional color reproduction."</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>No grammar, spelling, or punctuation errors are present.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The tone is friendly and product‑focused without hype, e.g., "Plus, enjoy peace of mind with the included 3‑year warranty."</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>The tone is friendly, credible, and persuasive, suitable for e‑commerce product marketing.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>The description contains 60 words, which falls within the 50‑90 word range.</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>The description contains 65 words, which falls within the 50‑90 word range.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>All claims match the source: "27" monitor boasts a crisp 2560x1440 IPS display, covering 100% of the sRGB color gamut and Calman Verified" and "lightweight design and durable metal stand" plus the "3‑year warranty".</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>All claims (27‑inch 2560×1440 IPS, 100% sRGB, Calman Verified, lightweight design, metal stand, 3‑year warranty) are directly supported by the provided product information.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
           <t>PASS</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fluency_single_explanation</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fluency_single_verdict</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>grammar_single_explanation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>grammar_single_verdict</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tone_single_explanation</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tone_single_verdict</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>length_single_explanation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>length_single_verdict</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>grounding_single_explanation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>grounding_single_verdict</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>single_judge_final_score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fluency</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>grammar</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tone</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>grounding</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>final_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 Pro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The description reads smoothly with natural phrasing, e.g., "Experience the power and elegance of the iPhone 15 Pro. Fueled by the blazing-fast A17 Pro chip and boasting a stunning 120Hz ProMotion display, this compact powerhouse delivers an unparalleled user experience." No awkward or repetitive phrasing is present.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors. For example, the sentence "Crafted with a durable titanium frame and protective Ceramic Shield glass, the iPhone 15 Pro is built to last." is well‑formed.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The description uses promotional language such as "blazing-fast A17 Pro chip" and "the ultimate choice for discerning users," which leans toward hype rather than a strictly balanced, credible tone. While the overall tone is persuasive and friendly, the presence of exaggerated phrasing makes it more than neutral, fitting the rubric's definition of a slightly overhyped description.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The description contains 76 words. This falls within the 50‑90 word range defined for a 'good' rating.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>The description states: "Fueled by the blazing-fast A17 Pro chip and boasting a stunning 120Hz ProMotion display, this compact powerhouse..." which directly matches the attributes "A17 Pro chip" and "120 Hz ProMotion display" and the dimension note "compact". It also says "Crafted with a durable titanium frame and protective Ceramic Shield glass," which aligns with the attributes "titanium frame, Ceramic Shield glass." The claim "enjoy the convenience of USB‑C fast charging" is supported by the attribute "USB‑C fast charging," and the mention of a "1‑year limited warranty" matches the warranty attribute. Every concrete claim is directly supported by the provided structured attributes, with no unsupported or inferred statements.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sony WH‑1000XM5 Headphones</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The description reads smoothly and naturally, e.g., "Escape into your own world of sound with the Sony WH-1000XM5 Headphones.  These premium headphones boast industry-leading active noise cancelling, so you can focus on your music, podcast, or audiobook without distractions." No awkward or repetitive phrasing is evident.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors; for example, the sentence "Escape into your own world of sound with the Sony WH-1000XM5 Headphones." is grammatically correct.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The description uses a friendly, credible voice and persuasive language without hype, e.g., "Escape into your own world of sound with the Sony WH-1000XM5 Headphones" and "you can experience audio excellence with confidence," which aligns with the tone rubric for a good rating.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The description contains 76 words, which is within the 50‑90 word range defined for a 'good' rating. The word count was verified by counting each token separated by spaces, resulting in the total of 76 words.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The description’s claims about "active noise cancelling," "up to 30 hours of battery life," "Bluetooth 5.2 connectivity," "synthetic leather earcups," and "1‑year limited warranty" all directly match the structured attributes. The phrase "industry‑leading active noise cancelling" adds a mild overstatement that is not explicitly supported by the attributes, which is a single soft overstatement.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amazon Echo Dot (5th Gen)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The description reads smoothly and naturally. Phrases such as "Meet the new Echo Dot, packed with smart features and sustainable style" and "This 5th generation Echo Dot boasts an improved bass for richer sound and even includes a temperature sensor for added convenience" are clear and free of awkward or repetitive wording.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors. All sentences are well‑formed, e.g., "Meet the new Echo Dot, packed with smart features and sustainable style." and "With Alexa, you can control your smart home, play music, get answers to questions, and more, all with just your voice.".</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The description uses a friendly, credible tone, e.g., “Meet the new Echo Dot, packed with smart features and sustainable style.” It conveys benefits persuasively without exaggerated hype, maintaining a balanced marketing style.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The description contains 80 words. Counting each word: 12 (first sentence) + 21 (second) + 21 (third) + 17 (fourth) + 9 (fifth) = 80 words, which falls within the 50‑90 word range defined for a 'good' rating.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>The description states: "With Alexa, you can control your smart home..." which aligns with the feature "Alexa voice assistant". It claims "improved bass for richer sound" matching the feature "improved bass". It mentions "includes a temperature sensor" which directly reflects the feature "temperature sensor". It describes the product as "crafted with a cozy recycled fabric mesh" which corresponds to the material attribute "recycled fabric mesh". Finally, it notes "a 1-year limited warranty" which matches the warranty attribute "1‑year limited warranty". All concrete claims are directly supported by the provided structured attributes, with no unsupported or inferred statements.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fitbit Charge 6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The description reads smoothly, e.g., "Enjoy up to 7 days of battery life on a single charge, so you can focus on your activity, not your charger." There are no awkward or repetitive phrases, and the flow is natural throughout.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors. For example, the sentence "Enjoy up to 7 days of battery life on a single charge, so you can focus on your activity, not your charger." is well‑formed and correctly punctuated.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The description uses a friendly, credible tone, offering clear benefits without exaggerated hype. Phrases like "Stay on top of your health and fitness goals with the Fitbit Charge 6" and "your reliable companion for a healthier, more active you" are persuasive yet grounded, meeting the rubric for a good tone.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The description contains 93 words. This falls into the 91‑110 word range, which the rubric classifies as “ok”.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>The description’s claims are all directly supported by the provided attributes: 
+- "aluminum tracker" matches the attribute "Material: aluminum case".
+- "built‑in GPS" matches the feature "built‑in GPS".
+- "heart‑rate monitor" matches the feature "heart‑rate monitor".
+- "up to 7 days of battery life" matches the feature "7‑day battery".
+- "multiple color options" matches the attribute "color options: multiple".
+- "1‑year limited warranty" matches the attribute "Warranty: 1‑year limited warranty".
+No claim is unsupported, inferred, or overstated.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DJI Mini 4 Pro Drone</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The description reads smoothly with natural phrasing throughout. For example, the phrase "Capture stunning 4K footage at 60fps with the DJI Mini 4 Pro!" flows naturally and there are no awkward or repetitive constructions.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>The description contains a minor formatting issue: there is a double space before the word "Omnidirectional" (".  Omnidirectional"). This does not affect readability significantly, but it is a minor punctuation error.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The description uses a friendly, persuasive tone, but includes a mildly hype phrase such as "Capture stunning 4K footage at 60fps" which introduces a slight exaggeration. It remains credible and suitable for product marketing, so it fits the 'acceptable but generic, flat, or slightly overhyped' category.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The description contains 55 words, which is within the 50‑90 word range defined for a 'good' rating. For example, the text includes: "Capture stunning 4K footage at 60fps with the DJI Mini 4 Pro! This lightweight drone, weighing under 250g, is perfect for adventurers and beginners alike. Omnidirectional obstacle sensing keeps you safe, while the durable composite plastic construction ensures lasting performance. Backed by a 1-year limited warranty, the Mini 4 Pro is ready to elevate your aerial photography." This count satisfies the length criterion.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The description states: "Capture stunning 4K footage at 60fps" which matches the attribute "features: 4K/60fps". It says: "weighing under 250g" which matches "&lt;250 g". It mentions: "Omnidirectional obstacle sensing" which matches the attribute "features: omnidirectional obstacle sensing". It claims: "durable composite plastic construction" which aligns with the attribute "Material: composite plastic" (the adjective “durable” is a mild inference but not a new feature). Finally, it notes: "Backed by a 1‑year limited warranty" which matches the attribute "Warranty: 1‑year limited warranty". All concrete claims are directly supported by the provided attributes, with no invented or unsupported statements.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Xbox Series X</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The description reads smoothly with natural phrasing. For example, the sentence "Boasting a 12 TFLOPS GPU and a blazing-fast 1TB SSD, this console delivers stunning 4K visuals at up to 120Hz for incredibly smooth gameplay." flows without awkwardness or repetition, and the rest of the text maintains the same level of fluency.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors. For example, the sentence "Boasting a 12 TFLOPS GPU and a blazing-fast 1TB SSD, this console delivers stunning 4K visuals at up to 120Hz for incredibly smooth gameplay." is well‑formed and correctly punctuated.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The description uses persuasive language but includes hype‑y phrases such as “blazing‑fast 1TB SSD” and “incredibly smooth gameplay,” which go beyond a neutral, credible tone. It is friendly and clear, but the exaggerated adjectives prevent it from being fully “good.”</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>The description contains 64 words, which is within the 50‑90 word range defined for a 'good' rating. The count was obtained by counting each token separated by spaces, including numbers and hyphenated words, resulting in the total of 64 words.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>The description says "Enjoy long-lasting battery life," but the provided attributes list only a "battery: long‑lasting" without any context that the Xbox Series X has a battery. The console is a stationary device and does not have a battery life claim in the source attributes, so this claim is unsupported.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Instant Pot Duo 6‑Quart</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The description reads well overall, but the phrase "crafted with durable 18/8 stainless steel, including a convenient inner pot" is a bit clunky, mixing material description with the inner pot in a way that feels slightly redundant.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The description is well‑written overall, but the final sentence ends without a period, e.g., "...who want delicious results with ease". This is a single punctuation error.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The description uses a friendly, conversational tone, e.g., “your kitchen's new best friend!” and presents persuasive claims without exaggerated hype, maintaining credibility about the product’s features and warranty.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The description contains 85 words, which falls within the 50‑90 word range defined for a 'good' rating.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>The description’s claims are directly supported by the structured attributes: 
+- "7‑in‑1 multicooker" matches the feature "7‑in‑1 multicooker".
+- "durable 18/8 stainless steel" matches the material "18/8 stainless steel".
+- "including a convenient inner pot" matches the feature "stainless steel inner pot".
+- "1000W heating element" matches the feature "1000 W heating".
+- "Backed by a 1‑year limited warranty" matches the warranty "1‑year limited warranty".
+All concrete statements are grounded in the provided attributes, with no unsupported or inferred claims.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LEGO Star Wars Millennium Falcon 75192</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The description reads smoothly with natural phrasing, e.g., "Embark on an epic LEGO adventure with the Millennium Falcon 75192!" and there are no awkward or repetitive phrases.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors. For example, the sentence "Built with durable ABS plastic bricks and backed by a lifetime guarantee for missing pieces, this set is a must-have for any Star Wars fan." is correctly constructed and punctuated.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The description uses enthusiastic language like “Embark on an epic LEGO adventure” and “incredible set,” which adds hype beyond a neutral, persuasive tone. While the overall tone is friendly and persuasive, the phrasing is slightly overhyped, matching the rubric’s definition of an acceptable but slightly overhyped tone.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>The description contains 71 words, which falls within the 50‑90 word range defined for a 'good' rating. The word count was obtained by counting each token separated by spaces, including numbers and punctuation attached to words (e.g., "75192!" counts as one word).</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>The description states: "7,541 pieces" which matches the attribute 'features: 7 541 pieces'. It also says "intricately designed interior" and "included minifigures", directly supported by the attributes 'detailed interior' and 'minifigs included'. The claim "Built with durable ABS plastic bricks" aligns with the attribute 'Material: ABS plastic bricks'. Finally, "backed by a lifetime guarantee for missing pieces" corresponds exactly to the attribute 'Warranty: lifetime replacement of missing bricks'. Every concrete claim is directly supported by the provided structured attributes, with no unsupported or inferred statements.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Eufy Video Doorbell Dual</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The description reads smoothly with natural phrasing throughout. For example, the sentence "Keep an eye on your home with the Eufy Video Doorbell Dual" is clear and idiomatic, and the rest of the text follows the same flow without any awkward or repetitive constructions.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors. For example, the sentence "Enjoy long-lasting battery life and peace of mind with the Eufy Video Doorbell Dual, backed by a 1-year limited warranty." is correctly formed and punctuated.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The description uses a friendly, credible voice, e.g., “Enjoy long‑lasting battery life and peace of mind with the Eufy Video Doorbell Dual,” and it persuades without over‑hype, presenting features plainly. This meets the rubric for a good tone.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>The description contains 81 words. This falls within the 50‑90 word range defined for a 'good' rating.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>The description states: "dual cameras" (matches the feature 'dual camera'), "2K resolution" (matches the feature '2K resolution'), "package detection feature alerts you when a package arrives" (matches the feature 'package detection'), "long‑lasting battery life" (matches the attribute 'battery: long‑lasting'), and "1‑year limited warranty" (matches the attribute 'warranty: 1‑year limited warranty'). Every concrete claim is directly supported by the provided product attributes with no overstatement or invented details.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ASUS ProArt PA278QV Monitor</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The description reads smoothly with natural phrasing throughout. For example, the opening sentence "The ASUS ProArt PA278QV is your gateway to stunning visuals and professional‑grade color accuracy." is clear and flows well, and no awkward or repetitive phrases are present.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The description contains no noticeable grammar, spelling, or punctuation errors. For example, the sentence "covering 100% of the sRGB color gamut and Calman Verified for exceptional color reproduction" is grammatically correct and the rest of the text reads smoothly.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The description uses a friendly, inviting tone (e.g., "your gateway to stunning visuals") while presenting concrete specifications and a warranty, which makes it credible and persuasive without resorting to exaggerated hype. The language stays professional and appropriate for product marketing.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The description contains exactly 60 words, which falls within the 50‑90 word range defined for a 'good' length. No words are missing or extra beyond this range.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>The description says the monitor “boasts a crisp 2560x1440 IPS display, covering 100% of the sRGB color gamut and Calman Verified,” which directly matches the structured attributes (features: 27″ 2560×1440 IPS, 100% sRGB, Calman Verified). It also mentions a “lightweight design” and a “metal stand,” which correspond to the attributes weight: light and material: metal stand. However, the claim that it “make it perfect for any workspace” is a soft, unsubstantiated overstatement not found in the source attributes, constituting a mild inference. Therefore, not all concrete claims are directly supported.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>manual_rows</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>full_rows</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>full_run_judge_model</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b-fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>joint_agreement_fluency</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>joint_agreement_grammar</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>joint_agreement_tone</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>joint_agreement_length</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>joint_agreement_grounding</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>single_agreement_fluency</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>single_agreement_grammar</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>single_agreement_tone</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>single_agreement_length</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>single_agreement_grounding</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>human_pass_count_manual</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>joint_pass_count_manual</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>single_pass_count_manual</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
